--- a/artfynd/A 14502-2024 artfynd.xlsx
+++ b/artfynd/A 14502-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1854338</v>
+        <v>113507752</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S. Storbrännkullen, ca 9 km NO Borgvattnet, NO Fullsjön, Jmt</t>
+          <t>Västvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548255.6120145246</v>
+        <v>548527</v>
       </c>
       <c r="R2" t="n">
-        <v>7038803.351887064</v>
+        <v>7038503</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,49 +757,33 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>i ca 100-150-årig gransumpskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>spridd på granar</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Noomi Berg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1854340</v>
+        <v>1854338</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -842,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548347.4279769184</v>
+        <v>548256</v>
       </c>
       <c r="R3" t="n">
-        <v>7038475.670791317</v>
+        <v>7038803</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +844,9 @@
           <t>2011-08-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,12 +865,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>i gammal granskog nära myr</t>
+          <t>i ca 100-150-årig gransumpskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>på gammal gran</t>
+          <t>spridd på granar</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,50 +888,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113507752</v>
+        <v>1854339</v>
       </c>
       <c r="B4" t="n">
-        <v>90279</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västvattnet, Jmt</t>
+          <t>S. Storbrännkullen, ca 9 km NO Borgvattnet, NO Fullsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548527</v>
+        <v>548351</v>
       </c>
       <c r="R4" t="n">
-        <v>7038503</v>
+        <v>7038591</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2011-08-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2011-08-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,22 +970,145 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>i ca 100-120-årig granskog med inslag av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>riklig på granar</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Noomi Berg</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Noomi Berg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1854340</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>S. Storbrännkullen, ca 9 km NO Borgvattnet, NO Fullsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>548347</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7038476</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2011-08-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2011-08-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>i gammal granskog nära myr</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>på gammal gran</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14502-2024 artfynd.xlsx
+++ b/artfynd/A 14502-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113507752</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1854338</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1854339</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,8 +1129,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1854340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>